--- a/testakten/kurpfalz-taxware-software-ip-insolvenz/01_Mandat/03_Chronologie.xlsx
+++ b/testakten/kurpfalz-taxware-software-ip-insolvenz/01_Mandat/03_Chronologie.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chronologie" sheetId="1" r:id="R575abea0084d4c14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fristen_und_Termine" sheetId="2" r:id="R3196fe0bb5b54200"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chronologie" sheetId="1" r:id="Re171d1e8c73447db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fristen_und_Termine" sheetId="2" r:id="R1c1e97fadf744f28"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -316,10 +316,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="37" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="43" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -511,111 +511,128 @@
         <x:v>Kurpfalz Taxware / Rhenusbank</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
-        <x:v>Bankvermerk</x:v>
+        <x:v>05_Finanzierung_Sicherheiten/19_Mahnung_Stillhaltebitte_und_Bankantwort.pdf</x:v>
       </x:c>
       <x:c r="E14" s="14" t="str">
-        <x:v>vollständige Liquiditätsunterlagen</x:v>
+        <x:v>insolvenzrechtliche Wirkung der erbetenen Stillhaltung</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="34" customHeight="1">
       <x:c r="A15" s="15" t="str">
-        <x:v>15.09.2026</x:v>
+        <x:v>19.08.2026</x:v>
       </x:c>
       <x:c r="B15" s="15" t="str">
-        <x:v>Eröffnung Insolvenzverfahren</x:v>
+        <x:v>Kündigung, Fälligstellung und Verwertungsanzeige</x:v>
       </x:c>
       <x:c r="C15" s="15" t="str">
-        <x:v>AG Heidelberg / Dr. Mohn</x:v>
+        <x:v>Rhenusbank / Kurpfalz Taxware / vorläufige Verwalterin</x:v>
       </x:c>
       <x:c r="D15" s="15" t="str">
-        <x:v>06_Insolvenz_AssetDeal/01_Insolvenzeroeffnungsbeschluss_AG_Heidelberg.pdf</x:v>
+        <x:v>05_Finanzierung_Sicherheiten/20_Kuendigung_Faelligstellung_Verwertungsanzeige.pdf</x:v>
       </x:c>
       <x:c r="E15" s="15" t="str">
-        <x:v>Rechtskraftvermerk</x:v>
+        <x:v>Durchsetzung und Erlöszuordnung bleiben rechtlich zu prüfen</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
       <x:c r="A16" s="14" t="str">
-        <x:v>07.10.2026</x:v>
+        <x:v>15.09.2026</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
-        <x:v>Open-Source-Scan exportiert</x:v>
+        <x:v>Eröffnung Insolvenzverfahren</x:v>
       </x:c>
       <x:c r="C16" s="14" t="str">
-        <x:v>Verwalterteam / CodeAudit Süd</x:v>
+        <x:v>AG Heidelberg / Dr. Mohn</x:v>
       </x:c>
       <x:c r="D16" s="14" t="str">
-        <x:v>02_Unternehmen_Produkt/06_SBOM_Open_Source.xlsx</x:v>
+        <x:v>06_Insolvenz_AssetDeal/01_Insolvenzeroeffnungsbeschluss_AG_Heidelberg.pdf</x:v>
       </x:c>
       <x:c r="E16" s="14" t="str">
-        <x:v>AGPL-Treffer</x:v>
+        <x:v>Rechtskraftvermerk</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="34" customHeight="1">
       <x:c r="A17" s="15" t="str">
-        <x:v>12.10.2026</x:v>
+        <x:v>07.10.2026</x:v>
       </x:c>
       <x:c r="B17" s="15" t="str">
-        <x:v>Bewertung abgeschlossen</x:v>
+        <x:v>Open-Source-Scan exportiert</x:v>
       </x:c>
       <x:c r="C17" s="15" t="str">
-        <x:v>Bergstraße Advisory</x:v>
+        <x:v>Verwalterteam / CodeAudit Süd</x:v>
       </x:c>
       <x:c r="D17" s="15" t="str">
-        <x:v>06_Insolvenz_AssetDeal/03_Bewertung_Software_und_Vertraege.pdf</x:v>
+        <x:v>02_Unternehmen_Produkt/06_SBOM_Open_Source.xlsx</x:v>
       </x:c>
       <x:c r="E17" s="15" t="str">
-        <x:v>Annahmen zur Rechtekette</x:v>
+        <x:v>AGPL-Treffer</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="34" customHeight="1">
       <x:c r="A18" s="14" t="str">
-        <x:v>19.10.2026</x:v>
+        <x:v>12.10.2026</x:v>
       </x:c>
       <x:c r="B18" s="14" t="str">
-        <x:v>APA beiderseits unterzeichnet</x:v>
+        <x:v>Bewertung abgeschlossen</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
-        <x:v>Dr. Mohn / Weinberg Digital</x:v>
+        <x:v>Bergstraße Advisory</x:v>
       </x:c>
       <x:c r="D18" s="14" t="str">
-        <x:v>06_Insolvenz_AssetDeal/04_Asset_Purchase_Agreement_unterschrieben.docx</x:v>
+        <x:v>06_Insolvenz_AssetDeal/03_Bewertung_Software_und_Vertraege.pdf</x:v>
       </x:c>
       <x:c r="E18" s="14" t="str">
-        <x:v>Vollzugsvoraussetzungen</x:v>
+        <x:v>Annahmen zur Rechtekette</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="34" customHeight="1">
       <x:c r="A19" s="15" t="str">
-        <x:v>21.10.2026</x:v>
+        <x:v>19.10.2026</x:v>
       </x:c>
       <x:c r="B19" s="15" t="str">
-        <x:v>APA an Bank übersandt</x:v>
+        <x:v>APA beiderseits unterzeichnet</x:v>
       </x:c>
       <x:c r="C19" s="15" t="str">
-        <x:v>Dr. Mohn / Rhenusbank</x:v>
+        <x:v>Dr. Mohn / Weinberg Digital</x:v>
       </x:c>
       <x:c r="D19" s="15" t="str">
-        <x:v>06_Insolvenz_AssetDeal/06_Mail_Verwalter_Vollzug.eml</x:v>
+        <x:v>06_Insolvenz_AssetDeal/04_Asset_Purchase_Agreement_unterschrieben.docx</x:v>
       </x:c>
       <x:c r="E19" s="15" t="str">
-        <x:v>Zeitpunkt Datenraumzugang</x:v>
+        <x:v>Vollzugsvoraussetzungen</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="34" customHeight="1">
       <x:c r="A20" s="14" t="str">
+        <x:v>21.10.2026</x:v>
+      </x:c>
+      <x:c r="B20" s="14" t="str">
+        <x:v>APA an Bank übersandt</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="str">
+        <x:v>Dr. Mohn / Rhenusbank</x:v>
+      </x:c>
+      <x:c r="D20" s="14" t="str">
+        <x:v>06_Insolvenz_AssetDeal/06_Mail_Verwalter_Vollzug.eml</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="str">
+        <x:v>Zeitpunkt Datenraumzugang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="34" customHeight="1">
+      <x:c r="A21" s="15" t="str">
         <x:v>28.10.2026</x:v>
       </x:c>
-      <x:c r="B20" s="14" t="str">
+      <x:c r="B21" s="15" t="str">
         <x:v>angekündigtes Closing</x:v>
       </x:c>
-      <x:c r="C20" s="14" t="str">
+      <x:c r="C21" s="15" t="str">
         <x:v>Verwalterin / Erwerberin</x:v>
       </x:c>
-      <x:c r="D20" s="14" t="str">
+      <x:c r="D21" s="15" t="str">
         <x:v>06_Insolvenz_AssetDeal/05_Closing_Checkliste.xlsx</x:v>
       </x:c>
-      <x:c r="E20" s="14" t="str">
+      <x:c r="E21" s="15" t="str">
         <x:v>Übergabe und Freigaben</x:v>
       </x:c>
     </x:row>

--- a/testakten/kurpfalz-taxware-software-ip-insolvenz/01_Mandat/03_Chronologie.xlsx
+++ b/testakten/kurpfalz-taxware-software-ip-insolvenz/01_Mandat/03_Chronologie.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chronologie" sheetId="1" r:id="Re171d1e8c73447db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fristen_und_Termine" sheetId="2" r:id="R1c1e97fadf744f28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chronologie" sheetId="1" r:id="R076c574fe3224065"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fristen_und_Termine" sheetId="2" r:id="R46adf4e3a6fa471d"/>
   </x:sheets>
 </x:workbook>
 </file>
